--- a/AI_Recommendation_Logic/PCBuilder_Recommendation_Dataset.xlsx
+++ b/AI_Recommendation_Logic/PCBuilder_Recommendation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PIYUSH SAINI\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C9AEC8-54A7-4392-87F1-C2A13000C8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FD69BF-3C15-463E-91DC-2A59EFF6B809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6277,7 +6277,7 @@
         <v>230</v>
       </c>
       <c r="E71" s="2">
-        <v>254500</v>
+        <v>1200.25</v>
       </c>
       <c r="P71">
         <v>89</v>
@@ -6318,7 +6318,7 @@
         <v>234</v>
       </c>
       <c r="E72" s="2">
-        <v>452545</v>
+        <v>5002</v>
       </c>
       <c r="P72">
         <v>100</v>
@@ -6359,7 +6359,7 @@
         <v>236</v>
       </c>
       <c r="E73" s="2">
-        <v>240000</v>
+        <v>3200</v>
       </c>
       <c r="P73">
         <v>99.88</v>
